--- a/worked_examples/AIHE-CASE01_emergency_department_triage_portfolio_decision/workbook/xlsx/AIHE-CASE01_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE01_emergency_department_triage_portfolio_decision/workbook/xlsx/AIHE-CASE01_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Re0ba63ce9284436e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R91d74da27c4b4463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R6f1f9020d1014b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R3d1c6d8ed0a84eb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R6d783117ce1d4620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="Rfe761207b3e24c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R6f4b8b4c7a334496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="Re5dcec356e414545"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="36">
     <x:border/>
@@ -369,7 +385,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="118">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -378,7 +394,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -386,7 +402,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,22 +419,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -435,22 +451,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -495,22 +511,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -525,22 +541,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -611,6 +627,53 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -663,9 +726,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -774,25 +837,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Emergency-Department Triage Portfolio Decision</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="104" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -800,15 +863,15 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="106" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
-        <x:v>1: AI as a Health-System Intervention</x:v>
+        <x:v>1: AI as a Health System Intervention</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="106" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -816,7 +879,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="106" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -824,7 +887,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="106" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -832,7 +895,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="106" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -840,7 +903,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="106" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -848,7 +911,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="106" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -856,7 +919,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="108" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -889,54 +952,54 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
-      <x:c r="K1" s="5"/>
-      <x:c r="L1" s="5"/>
-      <x:c r="M1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
+      <x:c r="G1" s="102"/>
+      <x:c r="H1" s="102"/>
+      <x:c r="I1" s="102"/>
+      <x:c r="J1" s="102"/>
+      <x:c r="K1" s="102"/>
+      <x:c r="L1" s="102"/>
+      <x:c r="M1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Option</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Upfront cost</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="113" t="str">
         <x:v>Annual cost</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="113" t="str">
         <x:v>Wait-time reduction (min)</x:v>
       </x:c>
-      <x:c r="E3" s="58" t="str">
+      <x:c r="E3" s="113" t="str">
         <x:v>Adverse events avoided/year</x:v>
       </x:c>
-      <x:c r="F3" s="58" t="str">
+      <x:c r="F3" s="113" t="str">
         <x:v>Implementation months</x:v>
       </x:c>
-      <x:c r="G3" s="58" t="str">
+      <x:c r="G3" s="113" t="str">
         <x:v>Reversibility (1-5)</x:v>
       </x:c>
-      <x:c r="H3" s="59" t="str">
+      <x:c r="H3" s="114" t="str">
         <x:v>Equity risk (1-5)</x:v>
       </x:c>
-      <x:c r="I3" s="57" t="str">
+      <x:c r="I3" s="112" t="str">
         <x:v>Five-year cost</x:v>
       </x:c>
-      <x:c r="J3" s="58" t="str">
+      <x:c r="J3" s="113" t="str">
         <x:v>Benefit score</x:v>
       </x:c>
-      <x:c r="K3" s="59" t="str">
+      <x:c r="K3" s="114" t="str">
         <x:v>Decision score</x:v>
       </x:c>
     </x:row>
@@ -1115,40 +1178,40 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
+      <x:c r="G1" s="102"/>
+      <x:c r="H1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Option</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Upfront cost</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="113" t="str">
         <x:v>Annual cost</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="113" t="str">
         <x:v>Wait-time reduction (min)</x:v>
       </x:c>
-      <x:c r="E3" s="58" t="str">
+      <x:c r="E3" s="113" t="str">
         <x:v>Adverse events avoided/year</x:v>
       </x:c>
-      <x:c r="F3" s="58" t="str">
+      <x:c r="F3" s="113" t="str">
         <x:v>Implementation months</x:v>
       </x:c>
-      <x:c r="G3" s="58" t="str">
+      <x:c r="G3" s="113" t="str">
         <x:v>Reversibility (1-5)</x:v>
       </x:c>
-      <x:c r="H3" s="59" t="str">
+      <x:c r="H3" s="114" t="str">
         <x:v>Equity risk (1-5)</x:v>
       </x:c>
     </x:row>
@@ -1221,28 +1284,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Emergency-Department Triage Portfolio Decision</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="114" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1263,66 +1326,66 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="89" t="str">
+      <x:c r="A8" s="115" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B8" s="89"/>
-      <x:c r="C8" s="89"/>
-      <x:c r="D8" s="89"/>
-      <x:c r="E8" s="89"/>
-      <x:c r="F8" s="89"/>
+      <x:c r="B8" s="115"/>
+      <x:c r="C8" s="115"/>
+      <x:c r="D8" s="115"/>
+      <x:c r="E8" s="115"/>
+      <x:c r="F8" s="115"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="94" t="str">
+      <x:c r="A9" s="116" t="str">
         <x:v>Process redesign has the lowest five-year cost and strongest reversibility, while the combined option offers the greatest expected benefit but the highest implementation burden. The recommended sequence is to implement reversible process changes while conducting silent-mode local validation of the AI system. A combined pilot should proceed only after local calibration, response-capacity, audit, update, and exit conditions are satisfied.</x:v>
       </x:c>
-      <x:c r="B9" s="94"/>
-      <x:c r="C9" s="94"/>
-      <x:c r="D9" s="94"/>
-      <x:c r="E9" s="94"/>
-      <x:c r="F9" s="94"/>
+      <x:c r="B9" s="116"/>
+      <x:c r="C9" s="116"/>
+      <x:c r="D9" s="116"/>
+      <x:c r="E9" s="116"/>
+      <x:c r="F9" s="116"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="94"/>
-      <x:c r="B10" s="94"/>
-      <x:c r="C10" s="94"/>
-      <x:c r="D10" s="94"/>
-      <x:c r="E10" s="94"/>
-      <x:c r="F10" s="94"/>
+      <x:c r="A10" s="116"/>
+      <x:c r="B10" s="116"/>
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="116"/>
+      <x:c r="E10" s="116"/>
+      <x:c r="F10" s="116"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="94"/>
-      <x:c r="B11" s="94"/>
-      <x:c r="C11" s="94"/>
-      <x:c r="D11" s="94"/>
-      <x:c r="E11" s="94"/>
-      <x:c r="F11" s="94"/>
+      <x:c r="A11" s="116"/>
+      <x:c r="B11" s="116"/>
+      <x:c r="C11" s="116"/>
+      <x:c r="D11" s="116"/>
+      <x:c r="E11" s="116"/>
+      <x:c r="F11" s="116"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="94"/>
-      <x:c r="B12" s="94"/>
-      <x:c r="C12" s="94"/>
-      <x:c r="D12" s="94"/>
-      <x:c r="E12" s="94"/>
-      <x:c r="F12" s="94"/>
+      <x:c r="A12" s="116"/>
+      <x:c r="B12" s="116"/>
+      <x:c r="C12" s="116"/>
+      <x:c r="D12" s="116"/>
+      <x:c r="E12" s="116"/>
+      <x:c r="F12" s="116"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="94"/>
-      <x:c r="B13" s="94"/>
-      <x:c r="C13" s="94"/>
-      <x:c r="D13" s="94"/>
-      <x:c r="E13" s="94"/>
-      <x:c r="F13" s="94"/>
+      <x:c r="A13" s="116"/>
+      <x:c r="B13" s="116"/>
+      <x:c r="C13" s="116"/>
+      <x:c r="D13" s="116"/>
+      <x:c r="E13" s="116"/>
+      <x:c r="F13" s="116"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="100" t="str">
+      <x:c r="A15" s="117" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B15" s="100"/>
-      <x:c r="C15" s="100"/>
-      <x:c r="D15" s="100"/>
-      <x:c r="E15" s="100"/>
-      <x:c r="F15" s="100"/>
+      <x:c r="B15" s="117"/>
+      <x:c r="C15" s="117"/>
+      <x:c r="D15" s="117"/>
+      <x:c r="E15" s="117"/>
+      <x:c r="F15" s="117"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
